--- a/jogos_2026-02-13.xlsx
+++ b/jogos_2026-02-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="M2" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
         <v>3.19</v>
       </c>
-      <c r="N2" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.74</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="T2" t="n">
-        <v>3.01</v>
+        <v>2.73</v>
       </c>
       <c r="U2" t="n">
         <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>6.85</v>
+        <v>6.55</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
         <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46066.22916666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="M3" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="N3" t="n">
-        <v>2.97</v>
+        <v>3.09</v>
       </c>
       <c r="O3" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.19</v>
+        <v>3.74</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.73</v>
+        <v>3.01</v>
       </c>
       <c r="U3" t="n">
         <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>6.55</v>
+        <v>6.85</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
         <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.3</v>
+        <v>3.53</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46066.22916666666</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
-        <v>4.12</v>
+        <v>4.6</v>
       </c>
       <c r="N4" t="n">
-        <v>4.81</v>
+        <v>6.45</v>
       </c>
       <c r="O4" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="P4" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.19</v>
+        <v>5.97</v>
       </c>
       <c r="R4" t="n">
         <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="T4" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V4" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46066.23263888889</v>
@@ -1016,16 +1016,16 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="M5" t="n">
         <v>3.9</v>
       </c>
       <c r="N5" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
         <v>2.5</v>
@@ -1046,10 +1046,10 @@
         <v>1.78</v>
       </c>
       <c r="V5" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
@@ -1067,22 +1067,22 @@
         <v>2.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46066.32291666666</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>5.73</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46066.45833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46066.45833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.32</v>
+        <v>1.38</v>
       </c>
       <c r="M29" t="n">
-        <v>3.26</v>
+        <v>4.73</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>6.62</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="P29" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.55</v>
+        <v>5.76</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="S29" t="n">
-        <v>2.73</v>
+        <v>3.58</v>
       </c>
       <c r="T29" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="U29" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="V29" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.39</v>
+        <v>5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.94</v>
+        <v>1.46</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.14</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AF29" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.64</v>
+        <v>2.75</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46066.58333333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="M30" t="n">
-        <v>4.73</v>
+        <v>3.7</v>
       </c>
       <c r="N30" t="n">
-        <v>6.62</v>
+        <v>4.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="P30" t="n">
         <v>2.48</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.76</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="S30" t="n">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="U30" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="V30" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="W30" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z30" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AB30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC30" t="n">
         <v>2.38</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AD30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH30" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>2.75</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46066.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.58</v>
+        <v>2.32</v>
       </c>
       <c r="M31" t="n">
-        <v>3.7</v>
+        <v>3.26</v>
       </c>
       <c r="N31" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="O31" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="R31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V31" t="n">
+        <v>7</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y31" t="n">
         <v>1.27</v>
       </c>
-      <c r="S31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.15</v>
-      </c>
       <c r="Z31" t="n">
-        <v>4.1</v>
+        <v>3.39</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.54</v>
+        <v>1.94</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.2</v>
+        <v>1.64</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46066.58333333334</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5898,67 +5898,67 @@
         <v>2.05</v>
       </c>
       <c r="M46" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="N46" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O46" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="P46" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.98</v>
+        <v>5.17</v>
       </c>
       <c r="R46" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="S46" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="T46" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="U46" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="V46" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W46" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC46" t="n">
-        <v>5</v>
+        <v>5.65</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AH46" t="n">
         <v>1.63</v>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6017,67 +6017,67 @@
         <v>2.05</v>
       </c>
       <c r="M47" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="N47" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O47" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="P47" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="Q47" t="n">
-        <v>5.17</v>
+        <v>4.98</v>
       </c>
       <c r="R47" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="S47" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V47" t="n">
+        <v>10</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE47" t="n">
         <v>2.15</v>
       </c>
-      <c r="T47" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V47" t="n">
-        <v>13</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y47" t="n">
+      <c r="AF47" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z47" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AG47" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AH47" t="n">
         <v>1.63</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,73 +8989,73 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.74</v>
+        <v>2.08</v>
       </c>
       <c r="M72" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N72" t="n">
-        <v>2.05</v>
+        <v>3.06</v>
       </c>
       <c r="O72" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="P72" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="R72" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="S72" t="n">
-        <v>4.65</v>
+        <v>3.5</v>
       </c>
       <c r="T72" t="n">
-        <v>1.81</v>
+        <v>2.29</v>
       </c>
       <c r="U72" t="n">
-        <v>1.92</v>
+        <v>1.54</v>
       </c>
       <c r="V72" t="n">
-        <v>3.44</v>
+        <v>5</v>
       </c>
       <c r="W72" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="X72" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="Z72" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AB72" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.62</v>
+        <v>2.45</v>
       </c>
       <c r="AD72" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AF72" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG72" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH72" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AH72" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI72" s="3" t="n">
         <v>46066.66666666666</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,34 +9108,34 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.18</v>
+        <v>2.74</v>
       </c>
       <c r="M73" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="N73" t="n">
-        <v>14.44</v>
+        <v>2.05</v>
       </c>
       <c r="O73" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="P73" t="n">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="Q73" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="R73" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="S73" t="n">
-        <v>3.82</v>
+        <v>4.65</v>
       </c>
       <c r="T73" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U73" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="V73" t="n">
         <v>3.44</v>
@@ -9150,31 +9150,31 @@
         <v>1.06</v>
       </c>
       <c r="Z73" t="n">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB73" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AD73" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AF73" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="AG73" t="n">
-        <v>1.1</v>
+        <v>1.67</v>
       </c>
       <c r="AH73" t="n">
-        <v>3.98</v>
+        <v>1.4</v>
       </c>
       <c r="AI73" s="3" t="n">
         <v>46066.66666666666</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,73 +9227,73 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.35</v>
+        <v>1.44</v>
       </c>
       <c r="M74" t="n">
-        <v>3.24</v>
+        <v>4.75</v>
       </c>
       <c r="N74" t="n">
-        <v>2.03</v>
+        <v>5.25</v>
       </c>
       <c r="O74" t="n">
-        <v>4.42</v>
+        <v>1.85</v>
       </c>
       <c r="P74" t="n">
-        <v>2.14</v>
+        <v>2.63</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.45</v>
+        <v>5.3</v>
       </c>
       <c r="R74" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S74" t="n">
-        <v>2.91</v>
+        <v>3.96</v>
       </c>
       <c r="T74" t="n">
-        <v>2.53</v>
+        <v>2</v>
       </c>
       <c r="U74" t="n">
-        <v>1.43</v>
+        <v>1.72</v>
       </c>
       <c r="V74" t="n">
-        <v>5.95</v>
+        <v>4.2</v>
       </c>
       <c r="W74" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X74" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y74" t="n">
         <v>1.07</v>
       </c>
-      <c r="X74" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Z74" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="AB74" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="AC74" t="n">
-        <v>2.78</v>
+        <v>2.04</v>
       </c>
       <c r="AD74" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AF74" t="n">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="AG74" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.18</v>
+        <v>2.64</v>
       </c>
       <c r="AI74" s="3" t="n">
         <v>46066.66666666666</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,73 +9465,73 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="M76" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N76" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="O76" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P76" t="n">
         <v>2.5</v>
       </c>
-      <c r="P76" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Q76" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="R76" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S76" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T76" t="n">
         <v>2.25</v>
       </c>
       <c r="U76" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="V76" t="n">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="W76" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X76" t="n">
         <v>1.03</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z76" t="n">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="AA76" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD76" t="n">
         <v>1.57</v>
       </c>
-      <c r="AB76" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE76" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AF76" t="n">
-        <v>2.25</v>
+        <v>2.61</v>
       </c>
       <c r="AG76" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AI76" s="3" t="n">
         <v>46066.66666666666</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,73 +9584,73 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.08</v>
+        <v>3.35</v>
       </c>
       <c r="M77" t="n">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="N77" t="n">
-        <v>3.06</v>
+        <v>2.03</v>
       </c>
       <c r="O77" t="n">
-        <v>2.66</v>
+        <v>4.28</v>
       </c>
       <c r="P77" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="R77" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S77" t="n">
-        <v>3.5</v>
+        <v>3.19</v>
       </c>
       <c r="T77" t="n">
-        <v>2.29</v>
+        <v>2.53</v>
       </c>
       <c r="U77" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="V77" t="n">
-        <v>5</v>
+        <v>5.95</v>
       </c>
       <c r="W77" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X77" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z77" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AB77" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC77" t="n">
-        <v>2.45</v>
+        <v>2.78</v>
       </c>
       <c r="AD77" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AF77" t="n">
-        <v>2.38</v>
+        <v>2.09</v>
       </c>
       <c r="AG77" t="n">
         <v>1.23</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AI77" s="3" t="n">
         <v>46066.66666666666</v>
@@ -9703,10 +9703,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="M78" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N78" t="n">
         <v>3.5</v>
@@ -9718,34 +9718,34 @@
         <v>2.2</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.07</v>
+        <v>4.15</v>
       </c>
       <c r="R78" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S78" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="T78" t="n">
         <v>2.7</v>
       </c>
       <c r="U78" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V78" t="n">
         <v>6.95</v>
       </c>
       <c r="W78" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X78" t="n">
         <v>1.05</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z78" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="AA78" t="n">
         <v>1.87</v>
@@ -9757,19 +9757,19 @@
         <v>3.2</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG78" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AI78" s="3" t="n">
         <v>46066.66666666666</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,73 +9822,73 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="M79" t="n">
-        <v>4.75</v>
+        <v>7.4</v>
       </c>
       <c r="N79" t="n">
-        <v>5.25</v>
+        <v>14.44</v>
       </c>
       <c r="O79" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="P79" t="n">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="Q79" t="n">
-        <v>5.3</v>
+        <v>7.5</v>
       </c>
       <c r="R79" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S79" t="n">
-        <v>3.96</v>
+        <v>3.82</v>
       </c>
       <c r="T79" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="U79" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="V79" t="n">
-        <v>4.2</v>
+        <v>3.44</v>
       </c>
       <c r="W79" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="X79" t="n">
         <v>1.01</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z79" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AB79" t="n">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="AC79" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AD79" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AF79" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="AG79" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH79" t="n">
-        <v>2.64</v>
+        <v>3.98</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>46066.66666666666</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,73 +9941,73 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="M80" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O80" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P80" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q80" t="n">
         <v>3.5</v>
       </c>
-      <c r="N80" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O80" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P80" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>2.9</v>
-      </c>
       <c r="R80" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S80" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T80" t="n">
         <v>2.25</v>
       </c>
       <c r="U80" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="V80" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="W80" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X80" t="n">
         <v>1.03</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z80" t="n">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB80" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="AC80" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AF80" t="n">
-        <v>2.61</v>
+        <v>2.25</v>
       </c>
       <c r="AG80" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>46066.66666666666</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,73 +10060,73 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.15</v>
+        <v>1.56</v>
       </c>
       <c r="M81" t="n">
-        <v>3.45</v>
+        <v>3.93</v>
       </c>
       <c r="N81" t="n">
-        <v>3.05</v>
+        <v>4.87</v>
       </c>
       <c r="O81" t="n">
-        <v>2.61</v>
+        <v>2.14</v>
       </c>
       <c r="P81" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.58</v>
+        <v>4.6</v>
       </c>
       <c r="R81" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S81" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="T81" t="n">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="U81" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V81" t="n">
-        <v>5.3</v>
+        <v>5.65</v>
       </c>
       <c r="W81" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X81" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z81" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AB81" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AC81" t="n">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="AD81" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AF81" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AG81" t="n">
         <v>1.25</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>46066.67708333334</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,73 +10179,73 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.56</v>
+        <v>2.3</v>
       </c>
       <c r="M82" t="n">
-        <v>3.93</v>
+        <v>3.3</v>
       </c>
       <c r="N82" t="n">
-        <v>4.87</v>
+        <v>2.7</v>
       </c>
       <c r="O82" t="n">
-        <v>2.14</v>
+        <v>2.86</v>
       </c>
       <c r="P82" t="n">
         <v>2.3</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="R82" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S82" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="T82" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="U82" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V82" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="W82" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X82" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z82" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AB82" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AC82" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="AD82" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG82" t="n">
         <v>1.37</v>
       </c>
-      <c r="AE82" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG82" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH82" t="n">
-        <v>2.15</v>
+        <v>1.49</v>
       </c>
       <c r="AI82" s="3" t="n">
         <v>46066.67708333334</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,73 +10298,73 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="M83" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N83" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O83" t="n">
-        <v>2.86</v>
+        <v>2.61</v>
       </c>
       <c r="P83" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="R83" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S83" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="T83" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="U83" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V83" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="W83" t="n">
         <v>1.09</v>
       </c>
       <c r="X83" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z83" t="n">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="AA83" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH83" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AB83" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC83" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD83" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE83" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF83" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG83" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH83" t="n">
-        <v>1.49</v>
       </c>
       <c r="AI83" s="3" t="n">
         <v>46066.67708333334</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,73 +10536,73 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.25</v>
+        <v>1.66</v>
       </c>
       <c r="M85" t="n">
-        <v>3.37</v>
+        <v>3.8</v>
       </c>
       <c r="N85" t="n">
-        <v>2.12</v>
+        <v>4.52</v>
       </c>
       <c r="O85" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="W85" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AC85" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI85" s="3" t="n">
         <v>46066.6875</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,73 +10655,73 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.66</v>
+        <v>3.25</v>
       </c>
       <c r="M86" t="n">
-        <v>3.8</v>
+        <v>3.37</v>
       </c>
       <c r="N86" t="n">
-        <v>4.52</v>
+        <v>2.12</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W86" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AB86" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI86" s="3" t="n">
         <v>46066.6875</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,73 +10774,73 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="M87" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N87" t="n">
-        <v>3.83</v>
+        <v>7</v>
       </c>
       <c r="O87" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W87" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X87" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI87" s="3" t="n">
         <v>46066.69791666666</v>
@@ -10857,22 +10857,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,73 +10893,73 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.47</v>
+        <v>6.07</v>
       </c>
       <c r="M88" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="N88" t="n">
-        <v>5</v>
+        <v>1.44</v>
       </c>
       <c r="O88" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="P88" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q88" t="n">
         <v>2</v>
       </c>
-      <c r="P88" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>5</v>
-      </c>
       <c r="R88" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S88" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T88" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U88" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V88" t="n">
+        <v>7</v>
+      </c>
+      <c r="W88" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X88" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD88" t="n">
         <v>1.3</v>
       </c>
-      <c r="S88" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T88" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U88" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V88" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W88" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X88" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y88" t="n">
+      <c r="AE88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG88" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z88" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA88" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB88" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AC88" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD88" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE88" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF88" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG88" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH88" t="n">
-        <v>2.33</v>
+        <v>1.1</v>
       </c>
       <c r="AI88" s="3" t="n">
         <v>46066.69791666666</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,73 +11012,73 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W89" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X89" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC89" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD89" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI89" s="3" t="n">
         <v>46066.69791666666</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,73 +11131,73 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>3</v>
+        <v>1.59</v>
       </c>
       <c r="M90" t="n">
-        <v>3.39</v>
+        <v>3.95</v>
       </c>
       <c r="N90" t="n">
-        <v>2.19</v>
+        <v>5</v>
       </c>
       <c r="O90" t="n">
-        <v>3.32</v>
+        <v>2.05</v>
       </c>
       <c r="P90" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.63</v>
+        <v>5</v>
       </c>
       <c r="R90" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S90" t="n">
-        <v>3.18</v>
+        <v>2.94</v>
       </c>
       <c r="T90" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="U90" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V90" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="W90" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X90" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z90" t="n">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB90" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AC90" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD90" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AF90" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AG90" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AI90" s="3" t="n">
         <v>46066.69791666666</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,73 +11250,73 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="M91" t="n">
-        <v>3.89</v>
+        <v>3.35</v>
       </c>
       <c r="N91" t="n">
-        <v>5</v>
+        <v>3.83</v>
       </c>
       <c r="O91" t="n">
-        <v>2.15</v>
+        <v>2.51</v>
       </c>
       <c r="P91" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.85</v>
+        <v>4.64</v>
       </c>
       <c r="R91" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S91" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T91" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U91" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V91" t="n">
+        <v>8</v>
+      </c>
+      <c r="W91" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X91" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y91" t="n">
         <v>1.29</v>
       </c>
-      <c r="S91" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T91" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U91" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V91" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="W91" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X91" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z91" t="n">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AB91" t="n">
-        <v>2.07</v>
+        <v>1.72</v>
       </c>
       <c r="AC91" t="n">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="AD91" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AF91" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AG91" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AH91" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AI91" s="3" t="n">
         <v>46066.69791666666</v>
@@ -11333,22 +11333,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,73 +11369,73 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>6.25</v>
+        <v>1.65</v>
       </c>
       <c r="M92" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="N92" t="n">
-        <v>1.53</v>
+        <v>4.9</v>
       </c>
       <c r="O92" t="n">
-        <v>4.94</v>
+        <v>2.25</v>
       </c>
       <c r="P92" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q92" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="R92" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S92" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="T92" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="U92" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V92" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="W92" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X92" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z92" t="n">
-        <v>3.6</v>
+        <v>2.89</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AC92" t="n">
-        <v>3.05</v>
+        <v>3.79</v>
       </c>
       <c r="AD92" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AG92" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH92" t="n">
-        <v>1.14</v>
+        <v>2.1</v>
       </c>
       <c r="AI92" s="3" t="n">
         <v>46066.69791666666</v>
@@ -11452,22 +11452,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,73 +11488,73 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="M93" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="N93" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="O93" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P93" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q93" t="n">
         <v>4</v>
       </c>
-      <c r="P93" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>2.62</v>
-      </c>
       <c r="R93" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S93" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="T93" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="U93" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="V93" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="W93" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X93" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z93" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AB93" t="n">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AC93" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="AD93" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AF93" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="AG93" t="n">
-        <v>1.7</v>
+        <v>1.19</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="AI93" s="3" t="n">
         <v>46066.69791666666</v>
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,73 +11607,73 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.59</v>
+        <v>6.25</v>
       </c>
       <c r="M94" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="N94" t="n">
-        <v>5</v>
+        <v>1.53</v>
       </c>
       <c r="O94" t="n">
-        <v>2.05</v>
+        <v>4.94</v>
       </c>
       <c r="P94" t="n">
         <v>2.3</v>
       </c>
       <c r="Q94" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R94" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S94" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="T94" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U94" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="V94" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="W94" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X94" t="n">
         <v>1</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z94" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="AA94" t="n">
         <v>1.9</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AC94" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="AD94" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AG94" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH94" t="n">
-        <v>2.1</v>
+        <v>1.14</v>
       </c>
       <c r="AI94" s="3" t="n">
         <v>46066.69791666666</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,73 +11726,73 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="M95" t="n">
-        <v>3.5</v>
+        <v>3.39</v>
       </c>
       <c r="N95" t="n">
-        <v>4.9</v>
+        <v>2.19</v>
       </c>
       <c r="O95" t="n">
-        <v>2.25</v>
+        <v>3.32</v>
       </c>
       <c r="P95" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="Q95" t="n">
-        <v>5.5</v>
+        <v>2.63</v>
       </c>
       <c r="R95" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="S95" t="n">
-        <v>2.62</v>
+        <v>3.18</v>
       </c>
       <c r="T95" t="n">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="U95" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="V95" t="n">
-        <v>7.3</v>
+        <v>6</v>
       </c>
       <c r="W95" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X95" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z95" t="n">
-        <v>2.89</v>
+        <v>3.75</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AC95" t="n">
-        <v>3.79</v>
+        <v>2.88</v>
       </c>
       <c r="AD95" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.99</v>
+        <v>1.62</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.71</v>
+        <v>2.15</v>
       </c>
       <c r="AG95" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH95" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AI95" s="3" t="n">
         <v>46066.69791666666</v>
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,73 +11845,73 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="M96" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="N96" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V96" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W96" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG96" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH96" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI96" s="3" t="n">
         <v>46066.69791666666</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,73 +11964,73 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>6.07</v>
+        <v>1.6</v>
       </c>
       <c r="M97" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="N97" t="n">
-        <v>1.44</v>
+        <v>5</v>
       </c>
       <c r="O97" t="n">
-        <v>5.13</v>
+        <v>2.15</v>
       </c>
       <c r="P97" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q97" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="R97" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S97" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T97" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U97" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V97" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W97" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X97" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF97" t="n">
         <v>2</v>
-      </c>
-      <c r="R97" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S97" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T97" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U97" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V97" t="n">
-        <v>7</v>
-      </c>
-      <c r="W97" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X97" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y97" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z97" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA97" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB97" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC97" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AD97" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE97" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF97" t="n">
-        <v>1.7</v>
       </c>
       <c r="AG97" t="n">
         <v>1.18</v>
       </c>
       <c r="AH97" t="n">
-        <v>1.1</v>
+        <v>2.12</v>
       </c>
       <c r="AI97" s="3" t="n">
         <v>46066.69791666666</v>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,73 +12083,73 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U98" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V98" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH98" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI98" s="3" t="n">
         <v>46066.69791666666</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,73 +12202,73 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.25</v>
+        <v>2.82</v>
       </c>
       <c r="M99" t="n">
+        <v>3</v>
+      </c>
+      <c r="N99" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O99" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="P99" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>3</v>
+      </c>
+      <c r="R99" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S99" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T99" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U99" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V99" t="n">
+        <v>6</v>
+      </c>
+      <c r="W99" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X99" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC99" t="n">
         <v>3.1</v>
       </c>
-      <c r="N99" t="n">
-        <v>3</v>
-      </c>
-      <c r="O99" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="P99" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="R99" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S99" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T99" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U99" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V99" t="n">
-        <v>9</v>
-      </c>
-      <c r="W99" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X99" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y99" t="n">
+      <c r="AD99" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z99" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA99" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB99" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC99" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD99" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AE99" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AF99" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AG99" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AI99" s="3" t="n">
         <v>46066.70833333334</v>
@@ -12285,22 +12285,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,73 +12321,73 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.82</v>
+        <v>1.83</v>
       </c>
       <c r="M100" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="N100" t="n">
-        <v>2.49</v>
+        <v>5.23</v>
       </c>
       <c r="O100" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U100" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V100" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W100" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF100" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG100" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI100" s="3" t="n">
         <v>46066.70833333334</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,73 +12440,73 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="M101" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="N101" t="n">
-        <v>5.23</v>
+        <v>3</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S101" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U101" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V101" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W101" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG101" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH101" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI101" s="3" t="n">
         <v>46066.70833333334</v>
@@ -12916,22 +12916,22 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="M105" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N105" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="O105" t="n">
         <v>2.75</v>
       </c>
       <c r="P105" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q105" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="R105" t="n">
         <v>1.4</v>
@@ -12940,10 +12940,10 @@
         <v>2.32</v>
       </c>
       <c r="T105" t="n">
-        <v>2.99</v>
+        <v>3.09</v>
       </c>
       <c r="U105" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V105" t="n">
         <v>7.3</v>
@@ -12955,25 +12955,25 @@
         <v>1.06</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z105" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AA105" t="n">
         <v>2.1</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC105" t="n">
         <v>3.34</v>
       </c>
       <c r="AD105" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE105" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AF105" t="n">
         <v>1.91</v>
@@ -12982,7 +12982,7 @@
         <v>1.33</v>
       </c>
       <c r="AH105" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AI105" s="3" t="n">
         <v>46066.75</v>
@@ -13035,28 +13035,28 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="M106" t="n">
         <v>3.5</v>
       </c>
       <c r="N106" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="O106" t="n">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
       <c r="P106" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q106" t="n">
-        <v>2.63</v>
+        <v>2.94</v>
       </c>
       <c r="R106" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S106" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="T106" t="n">
         <v>2.73</v>
@@ -13083,7 +13083,7 @@
         <v>1.85</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC106" t="n">
         <v>3.3</v>
@@ -13092,7 +13092,7 @@
         <v>1.3</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AF106" t="n">
         <v>2.05</v>
@@ -13511,10 +13511,10 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="M110" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N110" t="n">
         <v>7.12</v>
@@ -13532,13 +13532,13 @@
         <v>1.6</v>
       </c>
       <c r="S110" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="T110" t="n">
         <v>3.1</v>
       </c>
       <c r="U110" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="V110" t="n">
         <v>10</v>
@@ -13559,7 +13559,7 @@
         <v>2.6</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AC110" t="n">
         <v>4.9</v>

--- a/jogos_2026-02-13.xlsx
+++ b/jogos_2026-02-13.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.48</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
-        <v>2.91</v>
+        <v>4.2</v>
       </c>
       <c r="N6" t="n">
-        <v>2.66</v>
+        <v>5.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46066.35416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>2.48</v>
       </c>
       <c r="M8" t="n">
-        <v>4.52</v>
+        <v>2.91</v>
       </c>
       <c r="N8" t="n">
-        <v>5.64</v>
+        <v>2.66</v>
       </c>
       <c r="O8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46066.35416666666</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>5.73</v>
+        <v>5.47</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46066.45833333334</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>12.68</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46066.45833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46066.58333333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="M29" t="n">
-        <v>4.73</v>
+        <v>5</v>
       </c>
       <c r="N29" t="n">
-        <v>6.62</v>
+        <v>8.35</v>
       </c>
       <c r="O29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.76</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46066.58333333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.58</v>
+        <v>2.32</v>
       </c>
       <c r="M30" t="n">
-        <v>3.7</v>
+        <v>3.26</v>
       </c>
       <c r="N30" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="R30" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V30" t="n">
+        <v>7</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y30" t="n">
         <v>1.27</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.15</v>
-      </c>
       <c r="Z30" t="n">
-        <v>4.1</v>
+        <v>3.39</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.54</v>
+        <v>1.94</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.2</v>
+        <v>1.64</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46066.58333333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.32</v>
+        <v>3.78</v>
       </c>
       <c r="M31" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="N31" t="n">
-        <v>2.8</v>
+        <v>2.08</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>4.45</v>
       </c>
       <c r="P31" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="Q31" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V31" t="n">
+        <v>9</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC31" t="n">
         <v>3.55</v>
       </c>
-      <c r="R31" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V31" t="n">
-        <v>7</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.14</v>
-      </c>
       <c r="AD31" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.64</v>
+        <v>1.21</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46066.58333333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>7.37</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46066.58333333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>6.62</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46066.58333333334</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="M35" t="n">
         <v>3.25</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,73 +4705,73 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
         <v>46066.58333333334</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,73 +4824,73 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.14</v>
+        <v>2.55</v>
       </c>
       <c r="M37" t="n">
-        <v>12</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>19</v>
+        <v>2.5</v>
       </c>
       <c r="O37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>7.37</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>46066.58333333334</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,73 +4943,73 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI38" s="3" t="n">
         <v>46066.58333333334</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,73 +5062,73 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.3</v>
+        <v>1.99</v>
       </c>
       <c r="M39" t="n">
-        <v>5</v>
+        <v>3.64</v>
       </c>
       <c r="N39" t="n">
-        <v>8.35</v>
+        <v>3.18</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI39" s="3" t="n">
         <v>46066.58333333334</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,73 +5181,73 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="M40" t="n">
-        <v>3.64</v>
+        <v>3.45</v>
       </c>
       <c r="N40" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="O40" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI40" s="3" t="n">
         <v>46066.58333333334</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,73 +5300,73 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.2</v>
+        <v>1.56</v>
       </c>
       <c r="M41" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>5</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S41" t="n">
         <v>3.25</v>
       </c>
-      <c r="N41" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AI41" s="3" t="n">
         <v>46066.58333333334</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,73 +5657,73 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="N44" t="n">
-        <v>3.7</v>
+        <v>3.51</v>
       </c>
       <c r="O44" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="P44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T44" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q44" t="n">
-        <v>4</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.33</v>
-      </c>
       <c r="U44" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="V44" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="W44" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X44" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.3</v>
+        <v>3.76</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC44" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF44" t="n">
         <v>2.23</v>
       </c>
-      <c r="AD44" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AG44" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH44" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AI44" s="3" t="n">
         <v>46066.60416666666</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,73 +5776,73 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M45" t="n">
-        <v>3.58</v>
+        <v>2.75</v>
       </c>
       <c r="N45" t="n">
-        <v>3.51</v>
+        <v>3.75</v>
       </c>
       <c r="O45" t="n">
-        <v>2.55</v>
+        <v>2.89</v>
       </c>
       <c r="P45" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="Q45" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T45" t="n">
         <v>3.9</v>
       </c>
-      <c r="R45" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U45" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="V45" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="W45" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.76</v>
+        <v>2.24</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.74</v>
+        <v>2.9</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.68</v>
+        <v>5.65</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.37</v>
+        <v>1.1</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.23</v>
+        <v>1.57</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AI45" s="3" t="n">
         <v>46066.60416666666</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,73 +5895,73 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="M46" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="N46" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O46" t="n">
-        <v>2.89</v>
+        <v>2.15</v>
       </c>
       <c r="P46" t="n">
-        <v>1.86</v>
+        <v>2.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.17</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>1.66</v>
+        <v>1.26</v>
       </c>
       <c r="S46" t="n">
-        <v>2.15</v>
+        <v>3.48</v>
       </c>
       <c r="T46" t="n">
-        <v>3.9</v>
+        <v>2.33</v>
       </c>
       <c r="U46" t="n">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="V46" t="n">
-        <v>13</v>
+        <v>5.05</v>
       </c>
       <c r="W46" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X46" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.24</v>
+        <v>4.3</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.9</v>
+        <v>1.61</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.36</v>
+        <v>2.25</v>
       </c>
       <c r="AC46" t="n">
-        <v>5.65</v>
+        <v>2.23</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.1</v>
+        <v>1.44</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AI46" s="3" t="n">
         <v>46066.60416666666</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,73 +6252,73 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="M49" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N49" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T49" t="n">
         <v>2.62</v>
       </c>
-      <c r="N49" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O49" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P49" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3.75</v>
-      </c>
       <c r="U49" t="n">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="V49" t="n">
-        <v>13</v>
+        <v>5.8</v>
       </c>
       <c r="W49" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X49" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AC49" t="n">
-        <v>6.5</v>
+        <v>3.05</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="AE49" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AI49" s="3" t="n">
         <v>46066.625</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,73 +6371,73 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="M50" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="N50" t="n">
-        <v>5.16</v>
+        <v>2.5</v>
       </c>
       <c r="O50" t="n">
-        <v>2.3</v>
+        <v>4.05</v>
       </c>
       <c r="P50" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="R50" t="n">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="S50" t="n">
-        <v>3.1</v>
+        <v>2.11</v>
       </c>
       <c r="T50" t="n">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="U50" t="n">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="V50" t="n">
-        <v>5.65</v>
+        <v>13</v>
       </c>
       <c r="W50" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="X50" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="Z50" t="n">
-        <v>4.26</v>
+        <v>2.21</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.92</v>
+        <v>2.8</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.07</v>
+        <v>1.36</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.85</v>
+        <v>6.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.73</v>
+        <v>2.26</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.05</v>
+        <v>1.34</v>
       </c>
       <c r="AI50" s="3" t="n">
         <v>46066.625</v>
@@ -6728,16 +6728,16 @@
         </is>
       </c>
       <c r="L53" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="M53" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O53" t="n">
         <v>6.5</v>
-      </c>
-      <c r="M53" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O53" t="n">
-        <v>7</v>
       </c>
       <c r="P53" t="n">
         <v>2.28</v>
@@ -6746,13 +6746,13 @@
         <v>2</v>
       </c>
       <c r="R53" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S53" t="n">
         <v>2.62</v>
       </c>
       <c r="T53" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U53" t="n">
         <v>1.36</v>
@@ -6770,13 +6770,13 @@
         <v>1.38</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AA53" t="n">
         <v>2.05</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC53" t="n">
         <v>3.54</v>
@@ -6794,7 +6794,7 @@
         <v>2.63</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AI53" s="3" t="n">
         <v>46066.64583333334</v>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,73 +6966,73 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="M55" t="n">
-        <v>2.74</v>
+        <v>3.55</v>
       </c>
       <c r="N55" t="n">
-        <v>5.58</v>
+        <v>4.6</v>
       </c>
       <c r="O55" t="n">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="P55" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q55" t="n">
-        <v>6.02</v>
+        <v>5.05</v>
       </c>
       <c r="R55" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="S55" t="n">
-        <v>2.62</v>
+        <v>2.93</v>
       </c>
       <c r="T55" t="n">
-        <v>3.18</v>
+        <v>2.78</v>
       </c>
       <c r="U55" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="V55" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="W55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X55" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.19</v>
+        <v>1.97</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.82</v>
+        <v>3.34</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="AI55" s="3" t="n">
         <v>46066.64583333334</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,73 +7085,73 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.72</v>
+        <v>3.2</v>
       </c>
       <c r="M56" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N56" t="n">
-        <v>4.6</v>
+        <v>2.05</v>
       </c>
       <c r="O56" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="P56" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.05</v>
+        <v>2.4</v>
       </c>
       <c r="R56" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="S56" t="n">
-        <v>2.93</v>
+        <v>3.32</v>
       </c>
       <c r="T56" t="n">
-        <v>2.78</v>
+        <v>2.25</v>
       </c>
       <c r="U56" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="V56" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W56" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X56" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z56" t="n">
-        <v>3.2</v>
+        <v>4.45</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC56" t="n">
-        <v>3.34</v>
+        <v>2.38</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.99</v>
+        <v>1.33</v>
       </c>
       <c r="AI56" s="3" t="n">
         <v>46066.64583333334</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7200,77 +7200,77 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI57" s="3" t="n">
         <v>46066.64583333334</v>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,73 +7323,73 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="P58" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="R58" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S58" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="T58" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="U58" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V58" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="W58" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X58" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z58" t="n">
         <v>2.88</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC58" t="n">
-        <v>3.58</v>
+        <v>3.84</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF58" t="n">
         <v>1.81</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AI58" s="3" t="n">
         <v>46066.64583333334</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,73 +7442,73 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O59" t="n">
-        <v>2.62</v>
+        <v>3.75</v>
       </c>
       <c r="P59" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="R59" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S59" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="T59" t="n">
-        <v>3.08</v>
+        <v>3.46</v>
       </c>
       <c r="U59" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="V59" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="W59" t="n">
         <v>1.01</v>
       </c>
       <c r="X59" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AC59" t="n">
-        <v>3.84</v>
+        <v>4.6</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AI59" s="3" t="n">
         <v>46066.64583333334</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7557,77 +7557,77 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI60" s="3" t="n">
         <v>46066.64583333334</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,73 +7680,73 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.2</v>
+        <v>1.82</v>
       </c>
       <c r="M61" t="n">
-        <v>3.6</v>
+        <v>2.74</v>
       </c>
       <c r="N61" t="n">
-        <v>2.05</v>
+        <v>5.58</v>
       </c>
       <c r="O61" t="n">
-        <v>3.6</v>
+        <v>2.59</v>
       </c>
       <c r="P61" t="n">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.4</v>
+        <v>6.02</v>
       </c>
       <c r="R61" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="S61" t="n">
-        <v>3.32</v>
+        <v>2.62</v>
       </c>
       <c r="T61" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="U61" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="V61" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X61" t="n">
         <v>1.1</v>
       </c>
-      <c r="X61" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y61" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="Z61" t="n">
-        <v>4.45</v>
+        <v>3.1</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.57</v>
+        <v>2.19</v>
       </c>
       <c r="AB61" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.38</v>
+        <v>3.82</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.46</v>
+        <v>1.23</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AF61" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AG61" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AI61" s="3" t="n">
         <v>46066.64583333334</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7799,40 +7799,40 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="M62" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N62" t="n">
-        <v>4.9</v>
+        <v>4.61</v>
       </c>
       <c r="O62" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="P62" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q62" t="n">
-        <v>5</v>
+        <v>5.28</v>
       </c>
       <c r="R62" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S62" t="n">
-        <v>2.55</v>
+        <v>2.77</v>
       </c>
       <c r="T62" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="U62" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V62" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="W62" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X62" t="n">
         <v>1.01</v>
@@ -7841,31 +7841,31 @@
         <v>1.32</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC62" t="n">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE62" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH62" t="n">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="AI62" s="3" t="n">
         <v>46066.64583333334</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,73 +7918,73 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.6</v>
+        <v>1.67</v>
       </c>
       <c r="M63" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>2.14</v>
+        <v>4.9</v>
       </c>
       <c r="O63" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="P63" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="R63" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S63" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="T63" t="n">
-        <v>3.46</v>
+        <v>3.08</v>
       </c>
       <c r="U63" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="V63" t="n">
-        <v>9.5</v>
+        <v>8.4</v>
       </c>
       <c r="W63" t="n">
         <v>1.01</v>
       </c>
       <c r="X63" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.44</v>
+        <v>2.11</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="AC63" t="n">
-        <v>4.6</v>
+        <v>3.82</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE63" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.29</v>
+        <v>2.01</v>
       </c>
       <c r="AI63" s="3" t="n">
         <v>46066.64583333334</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8046,64 +8046,64 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="AI64" s="3" t="n">
         <v>46066.66666666666</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.03</v>
+        <v>2.05</v>
       </c>
       <c r="M66" t="n">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="N66" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="O66" t="n">
         <v>2.5</v>
       </c>
-      <c r="O66" t="n">
-        <v>3.6</v>
-      </c>
       <c r="P66" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.25</v>
+        <v>4.55</v>
       </c>
       <c r="R66" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="S66" t="n">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="T66" t="n">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="U66" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="V66" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="W66" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="X66" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.45</v>
+        <v>3.05</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.68</v>
+        <v>2.17</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AC66" t="n">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.61</v>
+        <v>1.88</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>46066.66666666666</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,73 +8394,73 @@
         </is>
       </c>
       <c r="L67" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M67" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N67" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O67" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S67" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V67" t="n">
+        <v>11</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1</v>
+      </c>
+      <c r="X67" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z67" t="n">
         <v>2.52</v>
       </c>
-      <c r="M67" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N67" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O67" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="P67" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R67" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S67" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T67" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U67" t="n">
+      <c r="AA67" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH67" t="n">
         <v>1.36</v>
-      </c>
-      <c r="V67" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W67" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X67" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG67" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>1.42</v>
       </c>
       <c r="AI67" s="3" t="n">
         <v>46066.66666666666</v>
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,73 +8513,73 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="M68" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N68" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="O68" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="P68" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.74</v>
+        <v>3.28</v>
       </c>
       <c r="R68" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S68" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="T68" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="U68" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V68" t="n">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="W68" t="n">
         <v>1.05</v>
       </c>
       <c r="X68" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z68" t="n">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AC68" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AD68" t="n">
         <v>1.28</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AG68" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="AI68" s="3" t="n">
         <v>46066.66666666666</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,73 +8632,73 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="M69" t="n">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="N69" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O69" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="P69" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.55</v>
+        <v>4.74</v>
       </c>
       <c r="R69" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="S69" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="T69" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="U69" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="V69" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="W69" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X69" t="n">
         <v>1.02</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z69" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AC69" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AG69" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AI69" s="3" t="n">
         <v>46066.66666666666</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8760,64 +8760,64 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="AI70" s="3" t="n">
         <v>46066.66666666666</v>
@@ -8870,31 +8870,31 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.76</v>
+        <v>3.9</v>
       </c>
       <c r="M71" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="N71" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="O71" t="n">
         <v>4</v>
       </c>
       <c r="P71" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="R71" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S71" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="T71" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U71" t="n">
         <v>1.41</v>
@@ -8927,16 +8927,16 @@
         <v>1.28</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AG71" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH71" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AI71" s="3" t="n">
         <v>46066.66666666666</v>
@@ -8989,7 +8989,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="M72" t="n">
         <v>3.6</v>
@@ -9001,16 +9001,16 @@
         <v>2.66</v>
       </c>
       <c r="P72" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="R72" t="n">
         <v>1.28</v>
       </c>
       <c r="S72" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="T72" t="n">
         <v>2.29</v>
@@ -9028,7 +9028,7 @@
         <v>1.02</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z72" t="n">
         <v>4.6</v>
@@ -9046,10 +9046,10 @@
         <v>1.5</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AF72" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AG72" t="n">
         <v>1.23</v>
@@ -9111,10 +9111,10 @@
         <v>2.74</v>
       </c>
       <c r="M73" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="N73" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O73" t="n">
         <v>3</v>
@@ -9123,7 +9123,7 @@
         <v>2.55</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="R73" t="n">
         <v>1.14</v>
@@ -9147,22 +9147,22 @@
         <v>1.01</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Z73" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB73" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AD73" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AE73" t="n">
         <v>1.25</v>
@@ -9171,7 +9171,7 @@
         <v>3.5</v>
       </c>
       <c r="AG73" t="n">
-        <v>1.67</v>
+        <v>1.21</v>
       </c>
       <c r="AH73" t="n">
         <v>1.4</v>
@@ -9230,10 +9230,10 @@
         <v>1.44</v>
       </c>
       <c r="M74" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="N74" t="n">
-        <v>5.25</v>
+        <v>5.8</v>
       </c>
       <c r="O74" t="n">
         <v>1.85</v>
@@ -9248,7 +9248,7 @@
         <v>1.18</v>
       </c>
       <c r="S74" t="n">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="T74" t="n">
         <v>2</v>
@@ -9257,7 +9257,7 @@
         <v>1.72</v>
       </c>
       <c r="V74" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="W74" t="n">
         <v>1.16</v>
@@ -9275,16 +9275,16 @@
         <v>1.36</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AC74" t="n">
         <v>2.04</v>
       </c>
       <c r="AD74" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AF74" t="n">
         <v>2.48</v>
@@ -9293,7 +9293,7 @@
         <v>1.18</v>
       </c>
       <c r="AH74" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="AI74" s="3" t="n">
         <v>46066.66666666666</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,73 +9346,73 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.05</v>
+        <v>3.35</v>
       </c>
       <c r="M75" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="N75" t="n">
-        <v>3.12</v>
+        <v>2.03</v>
       </c>
       <c r="O75" t="n">
-        <v>2.63</v>
+        <v>4.28</v>
       </c>
       <c r="P75" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="R75" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S75" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="T75" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U75" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="V75" t="n">
-        <v>5.7</v>
+        <v>5.95</v>
       </c>
       <c r="W75" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X75" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y75" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH75" t="n">
         <v>1.2</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA75" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC75" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE75" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF75" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG75" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH75" t="n">
-        <v>1.61</v>
       </c>
       <c r="AI75" s="3" t="n">
         <v>46066.66666666666</v>
@@ -9468,7 +9468,7 @@
         <v>2.2</v>
       </c>
       <c r="M76" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="N76" t="n">
         <v>2.62</v>
@@ -9480,34 +9480,34 @@
         <v>2.5</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.9</v>
+        <v>3.37</v>
       </c>
       <c r="R76" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S76" t="n">
-        <v>3.7</v>
+        <v>3.36</v>
       </c>
       <c r="T76" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="U76" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="V76" t="n">
         <v>5</v>
       </c>
       <c r="W76" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X76" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z76" t="n">
-        <v>4.8</v>
+        <v>4.91</v>
       </c>
       <c r="AA76" t="n">
         <v>1.53</v>
@@ -9522,16 +9522,16 @@
         <v>1.57</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AF76" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AG76" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AI76" s="3" t="n">
         <v>46066.66666666666</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,73 +9584,73 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.35</v>
+        <v>1.95</v>
       </c>
       <c r="M77" t="n">
-        <v>3.24</v>
+        <v>3.55</v>
       </c>
       <c r="N77" t="n">
-        <v>2.03</v>
+        <v>3.5</v>
       </c>
       <c r="O77" t="n">
-        <v>4.28</v>
+        <v>2.55</v>
       </c>
       <c r="P77" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.45</v>
+        <v>4.15</v>
       </c>
       <c r="R77" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S77" t="n">
-        <v>3.19</v>
+        <v>2.91</v>
       </c>
       <c r="T77" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="U77" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V77" t="n">
-        <v>5.95</v>
+        <v>6.95</v>
       </c>
       <c r="W77" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X77" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y77" t="n">
         <v>1.25</v>
       </c>
       <c r="Z77" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AB77" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF77" t="n">
         <v>2</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE77" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF77" t="n">
-        <v>2.09</v>
       </c>
       <c r="AG77" t="n">
         <v>1.23</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.2</v>
+        <v>1.73</v>
       </c>
       <c r="AI77" s="3" t="n">
         <v>46066.66666666666</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,73 +9703,73 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="M78" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N78" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="O78" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P78" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q78" t="n">
         <v>3.5</v>
       </c>
-      <c r="O78" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P78" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>4.15</v>
-      </c>
       <c r="R78" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S78" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="T78" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U78" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="V78" t="n">
-        <v>6.95</v>
+        <v>5.7</v>
       </c>
       <c r="W78" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X78" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z78" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AC78" t="n">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AF78" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG78" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AI78" s="3" t="n">
         <v>46066.66666666666</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,73 +9822,73 @@
         </is>
       </c>
       <c r="L79" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M79" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N79" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O79" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P79" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S79" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V79" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W79" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X79" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y79" t="n">
         <v>1.18</v>
       </c>
-      <c r="M79" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="N79" t="n">
-        <v>14.44</v>
-      </c>
-      <c r="O79" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P79" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R79" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S79" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="T79" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U79" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V79" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="W79" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X79" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Z79" t="n">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AB79" t="n">
-        <v>3.65</v>
+        <v>2.2</v>
       </c>
       <c r="AC79" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH79" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE79" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF79" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG79" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>3.98</v>
       </c>
       <c r="AI79" s="3" t="n">
         <v>46066.66666666666</v>
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,73 +9941,73 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.01</v>
+        <v>1.22</v>
       </c>
       <c r="M80" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="N80" t="n">
-        <v>3.1</v>
+        <v>13</v>
       </c>
       <c r="O80" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="P80" t="n">
-        <v>2.4</v>
+        <v>2.71</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="R80" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="S80" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="T80" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="U80" t="n">
-        <v>1.52</v>
+        <v>1.87</v>
       </c>
       <c r="V80" t="n">
-        <v>5.15</v>
+        <v>3.25</v>
       </c>
       <c r="W80" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="X80" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="Z80" t="n">
-        <v>4.15</v>
+        <v>6.7</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AB80" t="n">
-        <v>2.22</v>
+        <v>3.28</v>
       </c>
       <c r="AC80" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.44</v>
+        <v>2.14</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AF80" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AG80" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.73</v>
+        <v>4.2</v>
       </c>
       <c r="AI80" s="3" t="n">
         <v>46066.66666666666</v>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,73 +10060,73 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.56</v>
+        <v>2.3</v>
       </c>
       <c r="M81" t="n">
-        <v>3.93</v>
+        <v>3.3</v>
       </c>
       <c r="N81" t="n">
-        <v>4.87</v>
+        <v>2.7</v>
       </c>
       <c r="O81" t="n">
-        <v>2.14</v>
+        <v>2.86</v>
       </c>
       <c r="P81" t="n">
         <v>2.3</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="R81" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S81" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="T81" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="U81" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V81" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="W81" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X81" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z81" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AB81" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AC81" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="AD81" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG81" t="n">
         <v>1.37</v>
       </c>
-      <c r="AE81" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF81" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG81" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH81" t="n">
-        <v>2.15</v>
+        <v>1.49</v>
       </c>
       <c r="AI81" s="3" t="n">
         <v>46066.67708333334</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,73 +10179,73 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.3</v>
+        <v>1.56</v>
       </c>
       <c r="M82" t="n">
-        <v>3.3</v>
+        <v>3.93</v>
       </c>
       <c r="N82" t="n">
-        <v>2.7</v>
+        <v>4.87</v>
       </c>
       <c r="O82" t="n">
-        <v>2.86</v>
+        <v>2.14</v>
       </c>
       <c r="P82" t="n">
         <v>2.3</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="R82" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S82" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="T82" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="U82" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V82" t="n">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="W82" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X82" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z82" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AB82" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH82" t="n">
         <v>2.15</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE82" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG82" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AH82" t="n">
-        <v>1.49</v>
       </c>
       <c r="AI82" s="3" t="n">
         <v>46066.67708333334</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,73 +10536,73 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.66</v>
+        <v>3.25</v>
       </c>
       <c r="M85" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N85" t="n">
-        <v>4.52</v>
+        <v>2.12</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W85" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI85" s="3" t="n">
         <v>46066.6875</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,73 +10655,73 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="M86" t="n">
-        <v>3.37</v>
+        <v>3.96</v>
       </c>
       <c r="N86" t="n">
-        <v>2.12</v>
+        <v>4.52</v>
       </c>
       <c r="O86" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V86" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="W86" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AC86" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI86" s="3" t="n">
         <v>46066.6875</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,73 +10774,73 @@
         </is>
       </c>
       <c r="L87" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M87" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N87" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O87" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P87" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R87" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S87" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T87" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U87" t="n">
         <v>1.33</v>
       </c>
-      <c r="M87" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N87" t="n">
-        <v>7</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" t="n">
-        <v>0</v>
-      </c>
       <c r="V87" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W87" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X87" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG87" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH87" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI87" s="3" t="n">
         <v>46066.69791666666</v>
@@ -10857,22 +10857,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,73 +10893,73 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>6.07</v>
+        <v>1.59</v>
       </c>
       <c r="M88" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="N88" t="n">
-        <v>1.44</v>
+        <v>5</v>
       </c>
       <c r="O88" t="n">
-        <v>5.13</v>
+        <v>2.05</v>
       </c>
       <c r="P88" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q88" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R88" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S88" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="T88" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="U88" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V88" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W88" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X88" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y88" t="n">
         <v>1.29</v>
       </c>
       <c r="Z88" t="n">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AC88" t="n">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="AD88" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE88" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AG88" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="AI88" s="3" t="n">
         <v>46066.69791666666</v>
@@ -10976,22 +10976,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,43 +11012,43 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="M89" t="n">
-        <v>3.5</v>
+        <v>3.39</v>
       </c>
       <c r="N89" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="O89" t="n">
-        <v>4</v>
+        <v>3.32</v>
       </c>
       <c r="P89" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R89" t="n">
         <v>1.33</v>
       </c>
       <c r="S89" t="n">
-        <v>3.04</v>
+        <v>3.18</v>
       </c>
       <c r="T89" t="n">
         <v>2.5</v>
       </c>
       <c r="U89" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V89" t="n">
         <v>6</v>
       </c>
       <c r="W89" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X89" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y89" t="n">
         <v>1.22</v>
@@ -11060,10 +11060,10 @@
         <v>1.8</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC89" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AD89" t="n">
         <v>1.36</v>
@@ -11075,7 +11075,7 @@
         <v>2.15</v>
       </c>
       <c r="AG89" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="AH89" t="n">
         <v>1.3</v>
@@ -11095,22 +11095,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,73 +11131,73 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.59</v>
+        <v>6.07</v>
       </c>
       <c r="M90" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="N90" t="n">
-        <v>5</v>
+        <v>1.44</v>
       </c>
       <c r="O90" t="n">
-        <v>2.05</v>
+        <v>5.13</v>
       </c>
       <c r="P90" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q90" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R90" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S90" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="T90" t="n">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="U90" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V90" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="W90" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X90" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y90" t="n">
         <v>1.29</v>
       </c>
       <c r="Z90" t="n">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AC90" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="AD90" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AG90" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH90" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="AI90" s="3" t="n">
         <v>46066.69791666666</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,73 +11250,73 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="M91" t="n">
-        <v>3.35</v>
+        <v>3.89</v>
       </c>
       <c r="N91" t="n">
-        <v>3.83</v>
+        <v>5</v>
       </c>
       <c r="O91" t="n">
-        <v>2.51</v>
+        <v>2.15</v>
       </c>
       <c r="P91" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="R91" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S91" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T91" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U91" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V91" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="W91" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X91" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF91" t="n">
         <v>2</v>
       </c>
-      <c r="Q91" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="R91" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S91" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T91" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U91" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V91" t="n">
-        <v>8</v>
-      </c>
-      <c r="W91" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X91" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z91" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA91" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB91" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC91" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD91" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE91" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF91" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AG91" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="AI91" s="3" t="n">
         <v>46066.69791666666</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,73 +11369,73 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="M92" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N92" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="O92" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V92" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W92" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI92" s="3" t="n">
         <v>46066.69791666666</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,73 +11607,73 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U94" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V94" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD94" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH94" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI94" s="3" t="n">
         <v>46066.69791666666</v>
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,73 +11726,73 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>3</v>
+        <v>1.47</v>
       </c>
       <c r="M95" t="n">
-        <v>3.39</v>
+        <v>4.1</v>
       </c>
       <c r="N95" t="n">
-        <v>2.19</v>
+        <v>5</v>
       </c>
       <c r="O95" t="n">
-        <v>3.32</v>
+        <v>2</v>
       </c>
       <c r="P95" t="n">
-        <v>2.29</v>
+        <v>2.54</v>
       </c>
       <c r="Q95" t="n">
-        <v>2.63</v>
+        <v>5</v>
       </c>
       <c r="R95" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S95" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="T95" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U95" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V95" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="W95" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X95" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AC95" t="n">
         <v>2.5</v>
       </c>
-      <c r="U95" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V95" t="n">
-        <v>6</v>
-      </c>
-      <c r="W95" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X95" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y95" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z95" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA95" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB95" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC95" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AD95" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AF95" t="n">
         <v>2.15</v>
       </c>
       <c r="AG95" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AH95" t="n">
-        <v>1.3</v>
+        <v>2.33</v>
       </c>
       <c r="AI95" s="3" t="n">
         <v>46066.69791666666</v>
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,73 +11845,73 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.47</v>
+        <v>6.43</v>
       </c>
       <c r="M96" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="N96" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="O96" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="P96" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q96" t="n">
         <v>2</v>
       </c>
-      <c r="P96" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>5</v>
-      </c>
       <c r="R96" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S96" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T96" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U96" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V96" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W96" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X96" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AD96" t="n">
         <v>1.3</v>
       </c>
-      <c r="S96" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T96" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U96" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V96" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="W96" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X96" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y96" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z96" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA96" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB96" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AC96" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD96" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AE96" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AF96" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AG96" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH96" t="n">
-        <v>2.33</v>
+        <v>1.13</v>
       </c>
       <c r="AI96" s="3" t="n">
         <v>46066.69791666666</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,73 +11964,73 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="M97" t="n">
-        <v>3.89</v>
+        <v>3.5</v>
       </c>
       <c r="N97" t="n">
-        <v>5</v>
+        <v>2.15</v>
       </c>
       <c r="O97" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="P97" t="n">
         <v>2.25</v>
       </c>
       <c r="Q97" t="n">
-        <v>4.85</v>
+        <v>2.62</v>
       </c>
       <c r="R97" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S97" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="T97" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="U97" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V97" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="W97" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X97" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z97" t="n">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AB97" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AC97" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="AD97" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AF97" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG97" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="AH97" t="n">
-        <v>2.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI97" s="3" t="n">
         <v>46066.69791666666</v>
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,73 +12083,73 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V98" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG98" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH98" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI98" s="3" t="n">
         <v>46066.69791666666</v>
@@ -12202,10 +12202,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="M99" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N99" t="n">
         <v>2.49</v>
@@ -12220,7 +12220,7 @@
         <v>3</v>
       </c>
       <c r="R99" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S99" t="n">
         <v>2.7</v>
@@ -12229,46 +12229,46 @@
         <v>2.62</v>
       </c>
       <c r="U99" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V99" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W99" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X99" t="n">
         <v>1.05</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z99" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA99" t="n">
         <v>1.83</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC99" t="n">
         <v>3.1</v>
       </c>
       <c r="AD99" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE99" t="n">
         <v>1.67</v>
       </c>
       <c r="AF99" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AG99" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AI99" s="3" t="n">
         <v>46066.70833333334</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,73 +12321,73 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="M100" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="N100" t="n">
-        <v>5.23</v>
+        <v>3</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U100" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V100" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W100" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG100" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH100" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI100" s="3" t="n">
         <v>46066.70833333334</v>
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,73 +12440,73 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="M101" t="n">
         <v>3.1</v>
       </c>
       <c r="N101" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O101" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="P101" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q101" t="n">
         <v>3</v>
       </c>
-      <c r="O101" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="P101" t="n">
+      <c r="R101" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S101" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T101" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="U101" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V101" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W101" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X101" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF101" t="n">
         <v>2</v>
       </c>
-      <c r="Q101" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="R101" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S101" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T101" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U101" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V101" t="n">
-        <v>9</v>
-      </c>
-      <c r="W101" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X101" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y101" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z101" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA101" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB101" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC101" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD101" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE101" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF101" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AG101" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AH101" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AI101" s="3" t="n">
         <v>46066.70833333334</v>
@@ -12523,22 +12523,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,73 +12559,73 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.94</v>
+        <v>1.83</v>
       </c>
       <c r="M102" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="N102" t="n">
-        <v>2.63</v>
+        <v>5.23</v>
       </c>
       <c r="O102" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="U102" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V102" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI102" s="3" t="n">
         <v>46066.70833333334</v>
@@ -12803,7 +12803,7 @@
         <v>3.2</v>
       </c>
       <c r="N104" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O104" t="n">
         <v>3.25</v>
@@ -12812,7 +12812,7 @@
         <v>2</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R104" t="n">
         <v>1.51</v>
@@ -12821,10 +12821,10 @@
         <v>2.39</v>
       </c>
       <c r="T104" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="U104" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="V104" t="n">
         <v>8</v>
@@ -12857,13 +12857,13 @@
         <v>1.85</v>
       </c>
       <c r="AF104" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG104" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH104" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI104" s="3" t="n">
         <v>46066.73958333334</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L107" t="n">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L109" t="n">
